--- a/vse-loti/341349729/spec-341349729.xlsx
+++ b/vse-loti/341349729/spec-341349729.xlsx
@@ -83,7 +83,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -95,6 +95,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -463,7 +466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -550,13 +553,13 @@
         <v>4.326</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>1676666.66</v>
+        <v>1374316.93</v>
       </c>
       <c r="H2" s="5" t="n">
+        <v>317687.69</v>
+      </c>
+      <c r="I2" s="5" t="n">
         <v>387578.98</v>
-      </c>
-      <c r="I2" s="5" t="n">
-        <v>465094.77</v>
       </c>
     </row>
     <row r="3">
@@ -585,13 +588,13 @@
         <v>1.732</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>656666.67</v>
+        <v>538251.37</v>
       </c>
       <c r="H3" s="5" t="n">
+        <v>310768.69</v>
+      </c>
+      <c r="I3" s="5" t="n">
         <v>379137.8</v>
-      </c>
-      <c r="I3" s="5" t="n">
-        <v>454965.36</v>
       </c>
     </row>
     <row r="4">
@@ -614,7 +617,7 @@
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" s="5" t="n">
-        <v>1233333.33</v>
+        <v>1010928.96</v>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
@@ -629,7 +632,7 @@
         <v>6.058</v>
       </c>
       <c r="G5" s="8" t="n">
-        <v>3566666.66</v>
+        <v>2923497.26</v>
       </c>
     </row>
     <row r="6">
@@ -639,21 +642,38 @@
         </is>
       </c>
       <c r="G6" s="8" t="n">
+        <v>2923497.26</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>НМЦК с НДС 22% (справочно):</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="n">
         <v>3566666.66</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="9" t="inlineStr">
         <is>
+          <t>Ставка НДС в документах не указана, расчёт справочный по 22 %; по ч. 1 ст. 22 44-ФЗ цена контракта включает налоги, поэтому сумма документа принята как цена с НДС. «с НДС» — сумма из документа, «без НДС» = сумма ÷ 1,22.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
           <t>Источник: Н(М)ЦК (2).doc</t>
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10"/>
+    <row r="11"/>
+    <row r="12"/>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A8:B10"/>
+    <mergeCell ref="A10:B12"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vse-loti/341349729/spec-341349729.xlsx
+++ b/vse-loti/341349729/spec-341349729.xlsx
@@ -466,7 +466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -478,6 +478,7 @@
     <col width="20.28515625" customWidth="1" min="7" max="7"/>
     <col width="18.85546875" customWidth="1" min="8" max="8"/>
     <col width="16.42578125" customWidth="1" min="9" max="9"/>
+    <col width="18.85546875" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -513,17 +514,22 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>Цена за т (без НДС)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>Стоимость (без НДС)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Цена за т (без НДС)</t>
-        </is>
-      </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Цена за т (с НДС)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Стоимость (с НДС)</t>
         </is>
       </c>
     </row>
@@ -553,13 +559,16 @@
         <v>4.326</v>
       </c>
       <c r="G2" s="5" t="n">
+        <v>317687.69</v>
+      </c>
+      <c r="H2" s="5" t="n">
         <v>1374316.93</v>
-      </c>
-      <c r="H2" s="5" t="n">
-        <v>317687.69</v>
       </c>
       <c r="I2" s="5" t="n">
         <v>387578.98</v>
+      </c>
+      <c r="J2" s="5" t="n">
+        <v>1676666.65</v>
       </c>
     </row>
     <row r="3">
@@ -588,13 +597,16 @@
         <v>1.732</v>
       </c>
       <c r="G3" s="5" t="n">
+        <v>310768.69</v>
+      </c>
+      <c r="H3" s="5" t="n">
         <v>538251.37</v>
-      </c>
-      <c r="H3" s="5" t="n">
-        <v>310768.69</v>
       </c>
       <c r="I3" s="5" t="n">
         <v>379137.8</v>
+      </c>
+      <c r="J3" s="5" t="n">
+        <v>656666.67</v>
       </c>
     </row>
     <row r="4">
@@ -616,11 +628,14 @@
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
-      <c r="G4" s="5" t="n">
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" s="5" t="n">
         <v>1010928.96</v>
       </c>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" s="5" t="n">
+        <v>1233333.33</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -632,7 +647,16 @@
         <v>6.058</v>
       </c>
       <c r="G5" s="8" t="n">
+        <v>482584.56</v>
+      </c>
+      <c r="H5" s="8" t="n">
         <v>2923497.26</v>
+      </c>
+      <c r="I5" s="8" t="n">
+        <v>588753.16</v>
+      </c>
+      <c r="J5" s="8" t="n">
+        <v>3566666.66</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +665,7 @@
           <t>НМЦК из обоснования:</t>
         </is>
       </c>
-      <c r="G6" s="8" t="n">
+      <c r="H6" s="8" t="n">
         <v>2923497.26</v>
       </c>
     </row>
@@ -651,7 +675,7 @@
           <t>НМЦК с НДС 22% (справочно):</t>
         </is>
       </c>
-      <c r="F7" s="8" t="n">
+      <c r="J7" s="8" t="n">
         <v>3566666.66</v>
       </c>
     </row>
